--- a/outputs/sota_benchmark.xlsx
+++ b/outputs/sota_benchmark.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jezva/work/rossum/emcoder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jezva/projects/python/emcoder/train/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3B5B1D7-DC0C-574D-A959-84050385314C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09F3668-C9F6-5847-BB6B-34C18BFA2114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="780" windowWidth="33120" windowHeight="21460" xr2:uid="{AA981B90-57E7-3745-AD00-BFA43C223FB4}"/>
   </bookViews>
@@ -86,15 +86,6 @@
     <t>125M</t>
   </si>
   <si>
-    <t>0.652</t>
-  </si>
-  <si>
-    <t>0.443</t>
-  </si>
-  <si>
-    <t>0.500</t>
-  </si>
-  <si>
     <t>149M</t>
   </si>
   <si>
@@ -113,7 +104,16 @@
     <t>ModernBERT-base</t>
   </si>
   <si>
-    <t>EmCoder (v1)</t>
+    <t>0.583</t>
+  </si>
+  <si>
+    <t>0.535</t>
+  </si>
+  <si>
+    <t>0.550</t>
+  </si>
+  <si>
+    <t>EmCoder</t>
   </si>
 </sst>
 </file>
@@ -529,16 +529,16 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -577,19 +577,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sota_benchmark.xlsx
+++ b/outputs/sota_benchmark.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jezva/projects/python/emcoder/train/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09F3668-C9F6-5847-BB6B-34C18BFA2114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D29AE9-EC37-E84D-9009-B112ECD12688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="780" windowWidth="33120" windowHeight="21460" xr2:uid="{AA981B90-57E7-3745-AD00-BFA43C223FB4}"/>
+    <workbookView xWindow="68840" yWindow="11620" windowWidth="38320" windowHeight="20920" xr2:uid="{AA981B90-57E7-3745-AD00-BFA43C223FB4}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -89,15 +89,6 @@
     <t>149M</t>
   </si>
   <si>
-    <t>0.408</t>
-  </si>
-  <si>
-    <t>0.495</t>
-  </si>
-  <si>
-    <t>0.440</t>
-  </si>
-  <si>
     <t>82.1M</t>
   </si>
   <si>
@@ -114,6 +105,15 @@
   </si>
   <si>
     <t>EmCoder</t>
+  </si>
+  <si>
+    <t>0.469</t>
+  </si>
+  <si>
+    <t>0.486</t>
+  </si>
+  <si>
+    <t>0.463</t>
   </si>
 </sst>
 </file>
@@ -526,19 +526,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -577,16 +577,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>

--- a/outputs/sota_benchmark.xlsx
+++ b/outputs/sota_benchmark.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jezva/projects/python/emcoder/train/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D29AE9-EC37-E84D-9009-B112ECD12688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698E0F6C-5D2C-AE49-B0EC-8F9CA5F40594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="68840" yWindow="11620" windowWidth="38320" windowHeight="20920" xr2:uid="{AA981B90-57E7-3745-AD00-BFA43C223FB4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Model</t>
   </si>
@@ -104,16 +104,13 @@
     <t>0.550</t>
   </si>
   <si>
-    <t>EmCoder</t>
-  </si>
-  <si>
-    <t>0.469</t>
-  </si>
-  <si>
-    <t>0.486</t>
-  </si>
-  <si>
-    <t>0.463</t>
+    <t>0.503</t>
+  </si>
+  <si>
+    <t>0.488</t>
+  </si>
+  <si>
+    <t>EmCoder V2</t>
   </si>
 </sst>
 </file>
@@ -526,16 +523,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
@@ -594,5 +591,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/outputs/sota_benchmark.xlsx
+++ b/outputs/sota_benchmark.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jezva/projects/python/emcoder/train/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698E0F6C-5D2C-AE49-B0EC-8F9CA5F40594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D37CD64-DB5B-8B44-994D-0580142F785F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68840" yWindow="11620" windowWidth="38320" windowHeight="20920" xr2:uid="{AA981B90-57E7-3745-AD00-BFA43C223FB4}"/>
+    <workbookView xWindow="12280" yWindow="5360" windowWidth="38320" windowHeight="20920" xr2:uid="{AA981B90-57E7-3745-AD00-BFA43C223FB4}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Model</t>
   </si>
@@ -89,9 +89,6 @@
     <t>149M</t>
   </si>
   <si>
-    <t>82.1M</t>
-  </si>
-  <si>
     <t>ModernBERT-base</t>
   </si>
   <si>
@@ -111,6 +108,24 @@
   </si>
   <si>
     <t>EmCoder V2</t>
+  </si>
+  <si>
+    <t>81.8M</t>
+  </si>
+  <si>
+    <t>F1 / M params</t>
+  </si>
+  <si>
+    <t>0.0060</t>
+  </si>
+  <si>
+    <t>0.0036</t>
+  </si>
+  <si>
+    <t>0.0037</t>
+  </si>
+  <si>
+    <t>0.0042</t>
   </si>
 </sst>
 </file>
@@ -498,13 +513,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7AD7288-EA41-CB49-95DC-AA3468F9232C}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,25 +535,31 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
+      <c r="F2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -554,8 +575,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -571,22 +595,28 @@
       <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
